--- a/output/pdf_financials_xlsx/CRB.xlsx
+++ b/output/pdf_financials_xlsx/CRB.xlsx
@@ -1333,40 +1333,40 @@
         <v>0.111168</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.312561</v>
+        <v>-0.312561</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.052359</v>
+        <v>-0.052359</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.06898</v>
+        <v>-0.06898</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.116238</v>
+        <v>-0.116238</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.165696</v>
+        <v>-0.165696</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.048684</v>
+        <v>-0.048684</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.079585</v>
+        <v>-0.079585</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.129766</v>
+        <v>-0.129766</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-1.414885</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.150013</v>
+        <v>-0.150013</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.292005</v>
+        <v>-0.292005</v>
       </c>
       <c r="P16" s="1" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.0616</v>
+        <v>-0.15873</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.222336</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1651,46 +1651,46 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.048565</v>
+        <v>-0.048565</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.111168</v>
+        <v>-0.111168</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.312561</v>
+        <v>-0.312561</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.052359</v>
+        <v>-0.052359</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.06898</v>
+        <v>-0.06898</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.116238</v>
+        <v>-0.116238</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.165696</v>
+        <v>-0.165696</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.048684</v>
+        <v>-0.048684</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.079585</v>
+        <v>-0.079585</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.129766</v>
+        <v>-0.129766</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-1.414885</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.150013</v>
+        <v>-0.150013</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.292005</v>
+        <v>-0.292005</v>
       </c>
       <c r="P20" s="1" t="inlineStr">
         <is>
@@ -1842,46 +1842,46 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.048565</v>
+        <v>-0.048565</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.111168</v>
+        <v>-0.111168</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.312561</v>
+        <v>-0.312561</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.052359</v>
+        <v>-0.052359</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.06898</v>
+        <v>-0.06898</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.116238</v>
+        <v>-0.116238</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.165696</v>
+        <v>-0.165696</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.048684</v>
+        <v>-0.048684</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.079585</v>
+        <v>-0.079585</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.129766</v>
+        <v>-0.129766</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-1.414885</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.150013</v>
+        <v>-0.150013</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.292005</v>
+        <v>-0.292005</v>
       </c>
       <c r="P23" s="1" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>28.414636</v>
+        <v>-28.414636</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2138,40 +2138,40 @@
         <v>0.111168</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.312561</v>
+        <v>-0.312561</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.052359</v>
+        <v>-0.052359</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.06898</v>
+        <v>-0.06898</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.116238</v>
+        <v>-0.116238</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.165696</v>
+        <v>-0.165696</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.048684</v>
+        <v>-0.048684</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.079585</v>
+        <v>-0.079585</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.129766</v>
+        <v>-0.129766</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.414885</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.150013</v>
+        <v>-0.150013</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.292005</v>
+        <v>-0.292005</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2268,40 +2268,40 @@
         <v>0.111168</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.312561</v>
+        <v>-0.312561</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.052359</v>
+        <v>-0.052359</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.06898</v>
+        <v>-0.06898</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.116238</v>
+        <v>-0.116238</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.165696</v>
+        <v>-0.165696</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.048684</v>
+        <v>-0.048684</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.079585</v>
+        <v>-0.079585</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.129766</v>
+        <v>-0.129766</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.385641</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.180781</v>
+        <v>-0.119245</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.323989</v>
+        <v>-0.260021</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2428,46 +2428,46 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>55.91612581128308</v>
+        <v>144.0838741887169</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="1" t="inlineStr">
         <is>
@@ -6358,55 +6358,55 @@
         <v>0.292273</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.29801</v>
+        <v>0.121059</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.29801</v>
+        <v>0.121059</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.121059</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.121059</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.121059</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.121059</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.121059</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.485637</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.510937</v>
       </c>
     </row>
     <row r="93">
@@ -10760,7 +10760,11 @@
           <t>Warrant reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -16426,7 +16430,11 @@
           <t>Warrant reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -19130,7 +19138,11 @@
           <t>Warrant reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -43520,10 +43532,10 @@
         </is>
       </c>
       <c r="Q339" s="5" t="n">
-        <v>0.150013</v>
+        <v>-0.150013</v>
       </c>
       <c r="R339" s="5" t="n">
-        <v>0.292005</v>
+        <v>-0.292005</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
@@ -47174,31 +47186,31 @@
         </is>
       </c>
       <c r="G375" s="5" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="H375" s="5" t="n">
-        <v>0.312561</v>
+        <v>-0.312561</v>
       </c>
       <c r="I375" s="5" t="n">
-        <v>0.052359</v>
+        <v>-0.052359</v>
       </c>
       <c r="J375" s="5" t="n">
-        <v>0.06898</v>
+        <v>-0.06898</v>
       </c>
       <c r="K375" s="5" t="n">
-        <v>0.116238</v>
+        <v>-0.116238</v>
       </c>
       <c r="L375" s="5" t="n">
-        <v>0.165696</v>
+        <v>-0.165696</v>
       </c>
       <c r="M375" s="5" t="n">
-        <v>0.048684</v>
+        <v>-0.048684</v>
       </c>
       <c r="N375" s="5" t="n">
-        <v>0.079585</v>
+        <v>-0.079585</v>
       </c>
       <c r="O375" s="5" t="n">
-        <v>0.129766</v>
+        <v>-0.129766</v>
       </c>
       <c r="P375" t="inlineStr">
         <is>
@@ -60430,13 +60442,13 @@
         </is>
       </c>
       <c r="E502" s="5" t="n">
-        <v>0.048565</v>
+        <v>-0.048565</v>
       </c>
       <c r="F502" s="5" t="n">
-        <v>0.111168</v>
+        <v>-0.111168</v>
       </c>
       <c r="G502" s="5" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="H502" t="inlineStr">
         <is>
@@ -60965,10 +60977,10 @@
         </is>
       </c>
       <c r="F507" s="5" t="n">
-        <v>0.111168</v>
+        <v>-0.111168</v>
       </c>
       <c r="G507" s="5" t="n">
-        <v>0.120429</v>
+        <v>-0.120429</v>
       </c>
       <c r="H507" t="inlineStr">
         <is>
@@ -62544,10 +62556,10 @@
         </is>
       </c>
       <c r="E522" s="5" t="n">
-        <v>0.048565</v>
+        <v>-0.048565</v>
       </c>
       <c r="F522" s="5" t="n">
-        <v>0.111168</v>
+        <v>-0.111168</v>
       </c>
       <c r="G522" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CRB.xlsx
+++ b/output/pdf_financials_xlsx/CRB.xlsx
@@ -1083,58 +1083,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022385</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005851</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004562</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008855999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010336</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012011</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007092</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002766</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001421</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002814</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-8.899999999999999e-05</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000216</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000112</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000477</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005801</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007161</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001702</v>
       </c>
     </row>
     <row r="13">
@@ -2132,46 +2132,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.110165</v>
+        <v>0.13255</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.111168</v>
+        <v>0.117019</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.120429</v>
+        <v>-0.115867</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.312561</v>
+        <v>-0.303705</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.052359</v>
+        <v>-0.042023</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.06898</v>
+        <v>-0.056969</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.116238</v>
+        <v>-0.109146</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.165696</v>
+        <v>-0.16293</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.048684</v>
+        <v>-0.047263</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.079585</v>
+        <v>-0.07677100000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.129766</v>
+        <v>-0.129677</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.414885</v>
+        <v>-1.414669</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.150013</v>
+        <v>-0.149933</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.292005</v>
+        <v>-0.291893</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2262,46 +2262,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.110165</v>
+        <v>0.13255</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.111168</v>
+        <v>0.117019</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.120429</v>
+        <v>-0.115867</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.312561</v>
+        <v>-0.303705</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.052359</v>
+        <v>-0.042023</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.06898</v>
+        <v>-0.056969</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.116238</v>
+        <v>-0.109146</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.165696</v>
+        <v>-0.16293</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.048684</v>
+        <v>-0.047263</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.079585</v>
+        <v>-0.07677100000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.129766</v>
+        <v>-0.129677</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.385641</v>
+        <v>-1.385425</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.119245</v>
+        <v>-0.119165</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.260021</v>
+        <v>-0.259909</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2640,19 +2640,19 @@
         <v>1.505082</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.956902</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.456311</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.166113</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.427444</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.070505</v>
       </c>
     </row>
     <row r="35">
@@ -2762,19 +2762,19 @@
         <v>1.505082</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.956902</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.456311</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.166113</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.427444</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.070505</v>
       </c>
     </row>
     <row r="37">
@@ -3494,19 +3494,19 @@
         <v>0.02</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.956902</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.456311</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.166113</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.449412</v>
+        <v>0.021968</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.227921</v>
+        <v>0.157416</v>
       </c>
     </row>
     <row r="49">
@@ -8330,25 +8330,25 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.035147</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.038677</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.039992</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.042279</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052549</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.064667</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.02299</v>
       </c>
     </row>
     <row r="125">
@@ -8391,25 +8391,25 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.035147</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.038677</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.039992</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.042279</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052549</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.064667</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.02299</v>
       </c>
     </row>
     <row r="126">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -22512,7 +22512,11 @@
           <t>Net lease payments</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -24846,7 +24850,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -37960,7 +37968,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -46864,7 +46872,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -60018,7 +60026,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRB.xlsx
+++ b/output/pdf_financials_xlsx/CRB.xlsx
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.15873</v>
+        <v>0.0616</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0.222336</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>144.0838741887169</v>
+        <v>55.91612581128308</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>200</v>
@@ -6797,7 +6797,7 @@
         <v>-0.129766</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-1.414885</v>
+        <v>1.414885</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>-0.150013</v>
@@ -7504,46 +7504,46 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001019</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000962</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000685</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000456</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000696</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000847</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000847</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000886</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000625</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001599</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.03815</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005127</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000883</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -7754,13 +7754,13 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.047192</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.043892</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.004523</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -7796,10 +7796,10 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.013221</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.056999</v>
       </c>
     </row>
     <row r="116">
@@ -8943,46 +8943,46 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001019</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000962</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000685</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000456</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000696</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000847</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000847</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000886</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000625</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001599</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.03815</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005127</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000883</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -9004,46 +9004,46 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0.007478</v>
+        <v>0.006459</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.13583</v>
+        <v>-0.136792</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.140171</v>
+        <v>-0.140856</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.206956</v>
+        <v>-0.207412</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.110698</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.107245</v>
+        <v>-0.107941</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.110759</v>
+        <v>-0.111606</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.115746</v>
+        <v>-0.116593</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.170663</v>
+        <v>-0.171549</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.177771</v>
+        <v>-0.178396</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.123766</v>
+        <v>-0.125365</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.14286</v>
+        <v>-0.18101</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.136167</v>
+        <v>-0.141294</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-0.137088</v>
+        <v>-0.137971</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.106141</v>
@@ -22126,7 +22126,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -23426,7 +23430,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E145" s="5" t="n">
         <v>-0.001019</v>
       </c>
@@ -25786,7 +25794,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -35288,7 +35300,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>-0.0616</v>
       </c>
@@ -61920,7 +61936,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E516" s="5" t="n">
         <v>-0.0616</v>
       </c>
